--- a/clients/foodistribute.com.au/meta-file.xlsx
+++ b/clients/foodistribute.com.au/meta-file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\invoi\fahad_projects\clients\foodistribute.com.au\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E852A123-959B-486A-9CE7-033A5798E2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36C5CD0-6C4E-4BEE-99A3-67A9B398DC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
